--- a/quality_surveys/044_line_length_input_form--quality_surveys.xlsx
+++ b/quality_surveys/044_line_length_input_form--quality_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -734,8 +734,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="36" customWidth="1" min="2" max="2"/>
-    <col width="36" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -763,12 +763,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_10,_'label':_'file_1'}</t>
+          <t>file_1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 10, 'label': 'File 1'}</t>
+          <t>File 1</t>
         </is>
       </c>
     </row>
@@ -780,12 +780,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_20,_'label':_'file_2'}</t>
+          <t>file_2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 20, 'label': 'File 2'}</t>
+          <t>File 2</t>
         </is>
       </c>
     </row>
@@ -797,12 +797,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_30,_'label':_'file_3'}</t>
+          <t>file_3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 30, 'label': 'File 3'}</t>
+          <t>File 3</t>
         </is>
       </c>
     </row>
@@ -814,12 +814,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_15,_'label':_'in_progress'}</t>
+          <t>in_progress</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 15, 'label': 'In Progress'}</t>
+          <t>In Progress</t>
         </is>
       </c>
     </row>
@@ -831,12 +831,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_25,_'label':_'complete'}</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 25, 'label': 'Complete'}</t>
+          <t>Complete</t>
         </is>
       </c>
     </row>
@@ -848,12 +848,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_35,_'label':_'cancelled'}</t>
+          <t>cancelled</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 35, 'label': 'Cancelled'}</t>
+          <t>Cancelled</t>
         </is>
       </c>
     </row>
@@ -865,12 +865,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_18,_'label':_'user_1'}</t>
+          <t>user_1</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 18, 'label': 'User 1'}</t>
+          <t>User 1</t>
         </is>
       </c>
     </row>
@@ -882,12 +882,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_28,_'label':_'user_2'}</t>
+          <t>user_2</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 28, 'label': 'User 2'}</t>
+          <t>User 2</t>
         </is>
       </c>
     </row>
@@ -899,12 +899,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_38,_'label':_'user_3'}</t>
+          <t>user_3</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 38, 'label': 'User 3'}</t>
+          <t>User 3</t>
         </is>
       </c>
     </row>
